--- a/data/600066_宇通客车_财务数据.xlsx
+++ b/data/600066_宇通客车_财务数据.xlsx
@@ -11378,7 +11378,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -18482,7 +18482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18512,8 +18512,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18560,22 +18558,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -18585,75 +18583,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -18687,58 +18675,52 @@
         <v>5.092093186953337</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>0.765934210916543</v>
+      <c r="J2" s="3" t="n">
+        <v>61.08835409910679</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>61.08835409910679</v>
+        <v>1.35088599969881</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.35088599969881</v>
+        <v>1.254354701069224</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1.254354701069224</v>
+        <v>156.9924702098107</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>2.215178079752842</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>162.5151509445086</v>
+        <v>16.38193205809672</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>16.38193205809672</v>
+        <v>1.019811174908119</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>21.97542992629316</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>1.019811174908119</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.332185427621419</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="V2" s="6" t="n">
+        <v>0.8609721556628454</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>3087000000</v>
+      </c>
       <c r="X2" s="6" t="n">
-        <v>0.8609721556628454</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>3087000000</v>
-      </c>
-      <c r="Z2" s="6" t="n">
         <v>0.8319283752334217</v>
       </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>2.517137270145431</v>
+      </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>2.517137270145431</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18775,63 +18757,57 @@
         <v>3.964214656492594</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.48128016883226</v>
+        <v>56.85054610811559</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>56.85054610811559</v>
+        <v>1.470673386232039</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.470673386232039</v>
+        <v>1.305865322753592</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.305865322753592</v>
+        <v>131.7442009483532</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>1.89531042397524</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>189.9424998913544</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>12.05581224724034</v>
       </c>
+      <c r="P3" s="6" t="n">
+        <v>0.931643706912604</v>
+      </c>
       <c r="Q3" s="3" t="n">
-        <v>29.86111533732673</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0.931643706912604</v>
-      </c>
+        <v>1.222698787922785</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.222698787922785</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>-7.331829473505075</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-22.77952485814113</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>-7.331829473505075</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>-22.77952485814113</v>
+        <v>2.875917392046424</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>-0.5521101755480502</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>2.875917392046424</v>
+        <v>-2479000000</v>
       </c>
       <c r="X3" s="6" t="n">
-        <v>-0.5521101755480502</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>-2479000000</v>
-      </c>
-      <c r="Z3" s="6" t="n">
         <v>0.8734586945462346</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>2.453527756494549</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>2.453527756494549</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18868,63 +18844,57 @@
         <v>5.868073627018182</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.022714800484675</v>
+        <v>54.46615397157532</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>54.46615397157532</v>
+        <v>1.573445850914205</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.573445850914205</v>
+        <v>1.357805907172996</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.357805907172996</v>
+        <v>119.616853664359</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>1.699228934741068</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>211.8607991187824</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>8.505084165646446</v>
       </c>
+      <c r="P4" s="6" t="n">
+        <v>0.8701782954141768</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>42.32762345305227</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0.8701782954141768</v>
-      </c>
+        <v>1.146080058242928</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>1.146080058242928</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>-4.443159562125977</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-26.49957536574897</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>-4.443159562125977</v>
+        <v>1.753076178625743</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-26.49957536574897</v>
+        <v>1.107207468987686</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.753076178625743</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>1.107207468987686</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>1520000000</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.9886648291095507</v>
       </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2.407840190322833</v>
+      </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>2.407840190322833</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18960,64 +18930,58 @@
       <c r="I5" s="3" t="n">
         <v>5.857926518262352</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>0.6937948720334238</v>
+      <c r="J5" s="3" t="n">
+        <v>51.7926224595434</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>51.7926224595434</v>
+        <v>1.665837982051904</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.665837982051904</v>
+        <v>1.399587678874606</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.399587678874606</v>
+        <v>107.4371291325233</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>1.869282953705861</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>192.5872160157982</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>7.033479375406128</v>
       </c>
+      <c r="P5" s="6" t="n">
+        <v>0.8296508683994286</v>
+      </c>
       <c r="Q5" s="3" t="n">
-        <v>51.18377132928079</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0.8296508683994286</v>
-      </c>
+        <v>1.099970907481828</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>1.099970907481828</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="3" t="n">
         <v>-3.950441543787966</v>
       </c>
+      <c r="T5" s="3" t="n">
+        <v>-15.62386794278564</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>-0.2527242588113808</v>
+      </c>
       <c r="V5" s="3" t="n">
-        <v>-15.62386794278564</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>-0.2527242588113808</v>
+        <v>2.724222564319526</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>4425000000</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>2.724222564319526</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>4425000000</v>
+        <v>1.240499742145791</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>1.240499742145791</v>
+        <v>2.433483580662612</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>2.433483580662612</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19053,64 +19017,58 @@
       <c r="I6" s="3" t="n">
         <v>7.150443949371235</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>0.3370063728817677</v>
+      <c r="J6" s="3" t="n">
+        <v>53.64133045148895</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>53.64133045148895</v>
+        <v>1.528205128205128</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.528205128205128</v>
+        <v>1.194072594072594</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.194072594072594</v>
+        <v>115.7093828919251</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>1.872254667464849</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>192.281534267698</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>4.699705329761905</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>76.60054721308202</v>
-      </c>
-      <c r="R6" s="6" t="n">
+      <c r="P6" s="6" t="n">
         <v>0.6199848141883515</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>0.8609868644725202</v>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="3" t="n">
+        <v>-28.81663742566378</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-73.62943846538221</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>-28.81663742566378</v>
+        <v>-9.24644472293358</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-73.62943846538221</v>
+        <v>6.887029591041809</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-9.24644472293358</v>
+        <v>2611000000</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.887029591041809</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>2611000000</v>
+        <v>1.298039033722008</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.298039033722008</v>
+        <v>1.961263939774509</v>
       </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>1.961263939774509</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19146,64 +19104,58 @@
       <c r="I7" s="3" t="n">
         <v>6.717765556787947</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>-0.5220259763283828</v>
+      <c r="J7" s="3" t="n">
+        <v>52.30056581483553</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>52.30056581483553</v>
+        <v>1.490021536252692</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.490021536252692</v>
+        <v>1.051687006460876</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.051687006460876</v>
+        <v>109.6460926807013</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>3.151154642867218</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>114.2438378309603</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>4.171739221179538</v>
       </c>
+      <c r="P7" s="6" t="n">
+        <v>0.7096570812138429</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>86.294943406892</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.7096570812138429</v>
-      </c>
+        <v>1.06326773062377</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.06326773062377</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>7.041748060614024</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>20.73741731480626</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>7.041748060614024</v>
+        <v>-3.440201729106617</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>20.73741731480626</v>
+        <v>1.144664578769262</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>-3.440201729106617</v>
+        <v>24000000</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.144664578769262</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>24000000</v>
+        <v>1.147568909176523</v>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>1.147568909176523</v>
+        <v>2.048204032849462</v>
       </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>2.048204032849462</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19239,64 +19191,58 @@
       <c r="I8" s="3" t="n">
         <v>7.7724532276875</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>-0.3589299839976681</v>
+      <c r="J8" s="3" t="n">
+        <v>51.34342289485966</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>51.34342289485966</v>
+        <v>1.510174880763116</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.510174880763116</v>
+        <v>1.121144674085851</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.121144674085851</v>
+        <v>105.5220608385859</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>4.338965088509156</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>82.96909347193987</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>3.84528755162</v>
       </c>
+      <c r="P8" s="6" t="n">
+        <v>0.7013371277482143</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>93.62108689331539</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.7013371277482143</v>
-      </c>
+        <v>1.096692690278714</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>1.096692690278714</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>-6.174295093079449</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>22.74844049185987</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>-6.174295093079449</v>
+        <v>-6.740036062923595</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>22.74844049185987</v>
+        <v>4.238056937490141</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-6.740036062923595</v>
+        <v>2278000000</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>4.238056937490141</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>2278000000</v>
+        <v>1.131751208115616</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>1.131751208115616</v>
+        <v>2.120169626461239</v>
       </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>2.120169626461239</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19332,64 +19278,58 @@
       <c r="I9" s="3" t="n">
         <v>5.797065041256601</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.3172952867880862</v>
+      <c r="J9" s="3" t="n">
+        <v>54.44469650322456</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>54.44469650322456</v>
+        <v>1.433352820812628</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.433352820812628</v>
+        <v>1.103551593101432</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1.103551593101432</v>
+        <v>119.5134096891229</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>6.310113054385719</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>57.05127576910672</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>5.227964511261827</v>
       </c>
+      <c r="P9" s="6" t="n">
+        <v>0.8887351735952674</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>68.86045213667873</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0.8887351735952674</v>
-      </c>
+        <v>1.400703900060603</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.400703900060603</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>24.05173799330958</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>139.5795862402003</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>24.05173799330958</v>
+        <v>2.863524234948997</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>139.5795862402003</v>
+        <v>2.564279167879344</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>2.863524234948997</v>
+        <v>4150000000</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>2.564279167879344</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>4150000000</v>
+        <v>1.124362540193475</v>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.124362540193475</v>
+        <v>2.290278475499345</v>
       </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>2.290278475499345</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19425,64 +19365,58 @@
       <c r="I10" s="3" t="n">
         <v>4.804902090304911</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>-0.2643680026238999</v>
+      <c r="J10" s="3" t="n">
+        <v>57.51920624552891</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>57.51920624552891</v>
+        <v>1.451514942370074</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.451514942370074</v>
+        <v>1.209055145282628</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.209055145282628</v>
+        <v>135.4004978767023</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>8.497165891340183</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>42.3670673967765</v>
+        <v>8.204723532785946</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>8.204723532785946</v>
+        <v>1.181360671789931</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>43.87716399723228</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>1.181360671789931</v>
-      </c>
+        <v>1.831348830314676</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.831348830314676</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>37.62887753337545</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>125.8177932487365</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>37.62887753337545</v>
+        <v>4.193537933045986</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>125.8177932487365</v>
+        <v>1.735948210348874</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>4.193537933045986</v>
+        <v>6515000000</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>1.735948210348874</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>6515000000</v>
+        <v>1.013929258805656</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>1.013929258805656</v>
+        <v>2.759896058371913</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>2.759896058371913</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19518,64 +19452,58 @@
       <c r="I11" s="3" t="n">
         <v>4.363742217832226</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>0.1017291672843487</v>
+      <c r="J11" s="3" t="n">
+        <v>51.97332525007579</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>51.97332525007579</v>
+        <v>1.807152635181383</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.807152635181383</v>
+        <v>1.504106776180698</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.504106776180698</v>
+        <v>108.2176218126736</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>8.245655649351114</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>43.65935412647627</v>
+        <v>10.20757396640114</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.20757396640114</v>
+        <v>1.271892478848651</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>35.26792959668599</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>1.271892478848651</v>
-      </c>
+        <v>1.965514861686712</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.965514861686712</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>11.30806095258675</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>35.41831559128486</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>11.30806095258675</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>35.41831559128486</v>
+        <v>2.609561133401749</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>0.5683377422149123</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>2.609561133401749</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>0.5683377422149123</v>
-      </c>
-      <c r="Y11" s="3" t="n">
         <v>2468000000</v>
       </c>
+      <c r="X11" s="3" t="n">
+        <v>1.04279482866112</v>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="n">
-        <v>1.04279482866112</v>
+        <v>3.325973256801572</v>
       </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>3.325973256801572</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>安全区</t>
         </is>
